--- a/怪物机制数值表.xlsx
+++ b/怪物机制数值表.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +33,23 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +96,41 @@
         <fgColor rgb="000891B2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E7EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -100,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -131,6 +181,54 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,313 +595,696 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>类型ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>颜色</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>体型</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>颜色(hex)</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>体型(size)</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>基础HP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>移速</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>金币</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>分数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>飞行</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>碰撞伤害</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>特殊属性</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>视觉特征</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="N1" s="11" t="inlineStr">
+        <is>
+          <t>出现条件</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>grunt</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>步兵</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>红色 #ef4444</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>zombie</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>炮灰</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>月球丧尸</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>#ef4444</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>红色方块+头顶红色小角</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>Wave 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>bomber</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>炮灰</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>自爆丧尸</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>#fb923c</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="I3" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>头顶红色小角</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>基础敌人，数量最多</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>fast</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>突击兵</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>粉色 #f472b6</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="K3" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>自爆(4m范围)</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
+        <is>
+          <t>橙色球体+闪烁发光</t>
+        </is>
+      </c>
+      <c r="N3" s="14" t="inlineStr">
+        <is>
+          <t>Wave 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>fatso</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>炮灰</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>胖子丧尸</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>#78716c</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>灰色大球体</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>Wave 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>swarm</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>炮灰</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>虫潮基底</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>#84cc16</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F5" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>绿色小方块</t>
+        </is>
+      </c>
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t>Wave 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>medic</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>队长</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>医疗特种队长</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>#22c55e</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>回血光环(10%)+远程射击</t>
+        </is>
+      </c>
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>绿色十字标记+治疗光环</t>
+        </is>
+      </c>
+      <c r="N6" s="17" t="inlineStr">
+        <is>
+          <t>Wave 6+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>shielder</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>队长</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>护盾特种队长</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>#3b82f6</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>护盾buff(减伤50%)+远程射击</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="inlineStr">
+        <is>
+          <t>蓝色护盾+护盾光环</t>
+        </is>
+      </c>
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <t>Wave 6+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>assassin</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>刺客精英</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>#ec4899</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>冲刺(×4速,CD3s)</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
+        <is>
+          <t>粉色尖锐体型+高速冲刺</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>Wave 10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>tankElite</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>坦克精英</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>#525252</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>冲刺(CD8s)</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="inlineStr">
+        <is>
+          <t>深灰大体型+厚重装甲</t>
+        </is>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t>Wave 10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>rangedElite</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>远程精英</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>#8b5cf6</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="F10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>激光球远程攻击</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>紫色+悬浮飞行</t>
+        </is>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>Wave 10+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>BOSS(毁灭核心)</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>#dc2626</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>50(基础)+Lv×50(spawnFinalBoss)</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>尖头锥形+粉色拖尾光</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>体型小速度极快，Wave3+出现</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>flyer</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>飞行兵</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>紫色 #a78bfa</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>两对紫色翅膀(拍打动画)+底部推进器</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>飞行单位(y=4~7)，无视地形，Wave5+出现</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>tank</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>重装兵</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>灰色 #78716c</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>前置蓝色半透明护盾+肩甲</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>高血量大体型，移速慢，Wave8+出现</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>boss</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>BOSS(毁灭核心)</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>深红 #dc2626</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>500+Lv×50</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>双角+发光眼+底部光环+周身光效</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>阶段二独有，有技能机制</t>
+      <c r="K11" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>技能AI(见Boss技能表)</t>
+        </is>
+      </c>
+      <c r="M11" s="19" t="inlineStr">
+        <is>
+          <t>深红巨体+双角+发光眼+底部光环+点光源</t>
+        </is>
+      </c>
+      <c r="N11" s="19" t="inlineStr">
+        <is>
+          <t>阶段二/Boss门</t>
         </is>
       </c>
     </row>
@@ -818,288 +1299,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>参数</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>值</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>基础出怪数</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>第一波基础怪物数量</t>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>第一波基础怪物数量(baseCount)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>增长因子</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="14" t="n">
         <v>1.22</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>每波数量 = 基础 × 1.22^(wave-1)</t>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>每波数量 = 30 × 1.22^(wave-1)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>前8波加成</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>×1.5</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>前8波额外增加50%出怪量</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>碰撞伤害(普通)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>怪物碰到玩家的伤害</t>
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>刷怪间隔</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>0.8-wave×0.03(最低0.12)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>波次越高刷怪越快</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>碰撞伤害(tank)</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>重装兵碰撞伤害</t>
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>波次系数(血量)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>1+(wave-1)×0.15</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>每波怪物血量增加15%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>碰撞伤害(Boss)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Boss碰撞伤害</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>击杀经验</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>10(base)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.expPerKillBase=10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>波次系数</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>1+(wave-1)×0.15</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>每波怪物血量增加15%</t>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>休整触发</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>每3波</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.restEveryNWaves=3</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>击杀经验系数</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>经验 = 分数×0.3×经验倍率</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>休整时长</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>20秒</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.restDuration=20</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>刷怪间隔</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>0.8-wave×0.03(最低0.12)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>波次越高刷怪越快</t>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Boss门解锁</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>第15波</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.bossUnlockWave=15</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>休整触发</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>每5波</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>每5波后进入休整期</t>
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>自动Boss波</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>第25波</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.bossWave=25</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>休整时长</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>20秒</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>休整期持续时间</t>
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>--- 出怪分配 ---</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr"/>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>--- 按概率分配 ---</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Boss门解锁</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>第15波</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>休整期可见Boss传送门</t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>炮灰比例</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>100%-队长%-精英%</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>剩余全部为炮灰</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Boss波次</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>第25波</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>自动进入Boss阶段</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  zombie</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>炮灰中35%为月球丧尸</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>fast出现</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Wave 3+</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>15%+(wave-3)×2%</t>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  swarm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>炮灰中20%为虫潮基底</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>flyer出现</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Wave 5+</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>8%+(wave-5)×1%</t>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  bomber</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>炮灰中20%为自爆丧尸</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>tank出现</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Wave 8+</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>5%+(wave-8)×1.5%</t>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  fatso</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>炮灰中25%为胖子丧尸</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>队长出现(Wave6+)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>min(10%, 3%+(wave-6)×1%)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>医疗/护盾各50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>精英出现(Wave10+)</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>min(12%, 2%+(wave-10)×1%)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>刺客/坦克/远程均匀分配</t>
         </is>
       </c>
     </row>
@@ -1114,175 +1633,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>触发条件</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>效果</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>追踪</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>默认阶段</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>阶段0(每7s循环)</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>正常追踪玩家</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>移速2.5</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>冲撞</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>每10s循环</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>阶段1(每7s循环)</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>锁定方向快速冲刺1.5秒</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>冲刺速度25</t>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>冲刺速度25，碰撞边界停止+爆炸，击退玩家</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>召唤尸潮</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>每10s循环</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>在身边召唤6只小怪(grunt/fast)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>阶段2(每7s循环)</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>在Boss身边召唤8只小怪(zombie/fast)</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>无直接伤害</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>每250ms召唤一只，带波次系数，紫色召唤光柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>AOE践踏</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>阶段3(每7s循环)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>14m范围内距离衰减伤害</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>最高20</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>先扣护盾再扣血，击退6力度，冲击波动画</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>护盾</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>HP&lt;50%且CD好</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>激活5秒，减少50%受到的伤害</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>小怪带波次系数</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>AOE践踏</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>每10s循环</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>12m范围内距离衰减伤害</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>最高25</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>先扣护盾再扣血</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>护盾</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>血量&lt;50%</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>激活5秒，减少50%受到的伤害</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>30秒CD，蓝色护盾球视觉效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>--- 基础属性 ---</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr"/>
+      <c r="C7" s="25" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr"/>
+      <c r="E7" s="24" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Boss体型</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>size=5</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>spawnFinalBoss中bossSize=5</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>30秒CD</t>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>ENEMY_TYPES中size=3.0(占位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Boss血量</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>500+Lv×50</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>spawnFinalBoss: 500+gameState.level*50</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>动态计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Boss金币</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>击杀奖励</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>spawnFinalBoss中</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Boss分数</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>击杀奖励</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>spawnFinalBoss中</t>
         </is>
       </c>
     </row>
@@ -1297,248 +1931,316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>参数</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>值</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>移动速度</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="14" t="n">
         <v>7.5</v>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>基础水平移动速度</t>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>基础水平移动速度(player.speed)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>冲刺倍率</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>×1.45</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Shift冲刺加速</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>近战加速</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>×1.4</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>持能量刀时移动加速</t>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>持能量刀时移动加速(WEAPONS[2].speedBonus)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>跳跃初速</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>垂直跳跃速度</t>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>垂直跳跃速度(player.jumpSpeed)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>下落加速度</t>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>下落加速度(player.gravity)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>基础HP</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>初始生命值</t>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>初始生命值(gameState.hp)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>基础护盾</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>自动回复，受击后4秒开始</t>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>自动回复，受击后4秒开始(gameState.shield)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>护盾回复</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>3/秒</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>4秒无伤后开始回复</t>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>4秒无伤后开始回复(gameState.shieldRegen)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>护盾回复延迟</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>4秒</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>受击后N秒才开始回复(gameState.shieldDelay)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>复活次数</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B11" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>阶段一最大复活次数(阶段二无复活)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>阶段一最大复活次数(CONFIG.maxRevives)，阶段二无复活</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>初始经验(Lv1→2)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>前5级经验减半</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B12" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.expBase=50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>经验增长率</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>×1.35/级</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Lv6+恢复正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.expGrowth=1.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>前5级经验</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>减半</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>前5级升级经验减半</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>升级奖励</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>+25金 +20HP +5%伤害</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>每次升级</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>竞技场半径</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B16" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>圆形竞技场</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>ARENA_RADIUS=40，圆形竞技场</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>出怪口</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B17" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>东南西北固定位置</t>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>东南西北4个固定出怪口(gateAngles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>休整间隔</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>每3波</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.restEveryNWaves=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>休整时长</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>20秒</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.restDuration=20</t>
         </is>
       </c>
     </row>

--- a/怪物机制数值表.xlsx
+++ b/怪物机制数值表.xlsx
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -229,6 +229,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,7 +616,7 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -711,10 +717,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>4</v>
@@ -771,10 +777,10 @@
         <v>0.9</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="H3" s="14" t="n">
         <v>5</v>
@@ -792,12 +798,12 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>自爆(4m范围)</t>
+          <t>自爆(8m范围)</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>橙色球体+闪烁发光</t>
+          <t>导弹造型(手雷壳体+尾翼+弹头)</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
@@ -831,10 +837,10 @@
         <v>1.8</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H4" s="14" t="n">
         <v>8</v>
@@ -891,10 +897,10 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="H5" s="14" t="n">
         <v>2</v>
@@ -951,10 +957,10 @@
         <v>1.2</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="H6" s="17" t="n">
         <v>25</v>
@@ -1011,10 +1017,10 @@
         <v>1.2</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>25</v>
@@ -1071,10 +1077,10 @@
         <v>0.8</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>35</v>
@@ -1131,10 +1137,10 @@
         <v>2.2</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="14" t="n">
         <v>40</v>
@@ -1191,10 +1197,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H10" s="14" t="n">
         <v>35</v>
@@ -1252,11 +1258,11 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>50(基础)+Lv×50(spawnFinalBoss)</t>
+          <t>75(基础)+Lv×50(spawnFinalBoss)</t>
         </is>
       </c>
       <c r="G11" s="19" t="n">
-        <v>2.5</v>
+        <v>0.54</v>
       </c>
       <c r="H11" s="19" t="n">
         <v>500</v>
@@ -1299,12 +1305,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1331,11 +1337,11 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
-          <t>第一波基础怪物数量(baseCount)</t>
+          <t>第一波基础怪物数量(baseCount=60,已翻倍)</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1356,7 @@
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>每波数量 = 30 × 1.22^(wave-1)</t>
+          <t>每波数量 = 60 × 1.22^(wave-1)</t>
         </is>
       </c>
     </row>
@@ -1459,164 +1465,196 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Boss门解锁</t>
+          <t>小波次间隔</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>第15波</t>
+          <t>5秒</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.bossUnlockWave=15</t>
+          <t>小波次之间5秒间隔</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>Boss门解锁</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>第15波</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>CONFIG.bossUnlockWave=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
           <t>自动Boss波</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>第25波</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>CONFIG.bossWave=25</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>--- 出怪分配 ---</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr"/>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>--- 按概率分配 ---</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>炮灰比例</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>100%-队长%-精英%</t>
-        </is>
+          <t>出怪口数量</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>8</v>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>剩余全部为炮灰</t>
+          <t>GATE_COUNT=8</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  zombie</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>炮灰中35%为月球丧尸</t>
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>--- 出怪分配 ---</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr"/>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>--- 按概率分配 ---</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  swarm</t>
+          <t>炮灰比例</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>100%-队长%-精英%</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>炮灰中20%为虫潮基底</t>
+          <t>剩余全部为炮灰</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  bomber</t>
+          <t xml:space="preserve">  zombie</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>~46%(权重55)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>炮灰中20%为自爆丧尸</t>
+          <t>炮灰中月球丧尸(+20%权重)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fatso</t>
+          <t xml:space="preserve">  swarm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>~17%(权重20)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>炮灰中25%为胖子丧尸</t>
+          <t>炮灰中虫潮基底(不变)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>队长出现(Wave6+)</t>
+          <t xml:space="preserve">  bomber</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>min(10%, 3%+(wave-6)×1%)</t>
+          <t>~33%(权重40)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>医疗/护盾各50%</t>
+          <t>炮灰中自爆丧尸(+20%权重)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  fatso</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>~4%(权重5)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>炮灰中胖子丧尸(-20%权重)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>队长出现(Wave6+)</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>min(10%, 3%+(wave-6)×1%)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>医疗/护盾各50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
           <t>精英出现(Wave10+)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>min(12%, 2%+(wave-10)×1%)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>刺客/坦克/远程均匀分配</t>
         </is>
@@ -1640,7 +1678,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1693,7 +1731,7 @@
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>移速2.5</t>
+          <t>移速0.54(已降为1/4)</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1775,7 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>在Boss身边召唤8只小怪(zombie/fast)</t>
+          <t>在Boss身边召唤8只小怪(zombie/swarm)</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
@@ -1866,7 +1904,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>动态计算</t>
+          <t>动态计算(ENEMY_TYPES中hp=75为占位)</t>
         </is>
       </c>
     </row>
@@ -1931,12 +1969,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1963,7 +2001,7 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
@@ -2121,11 +2159,11 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.expBase=50</t>
+          <t>CONFIG.expBase=30</t>
         </is>
       </c>
     </row>
@@ -2137,110 +2175,243 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>×1.35/级</t>
+          <t>×1.18/级</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.expGrowth=1.35</t>
+          <t>CONFIG.expGrowth=1.18(平滑曲线)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>前5级经验</t>
+          <t>升级奖励</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>减半</t>
+          <t>+25金 +20HP +5%伤害</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>前5级升级经验减半</t>
+          <t>每次升级</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>升级奖励</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>+25金 +20HP +5%伤害</t>
-        </is>
+          <t>竞技场半径</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>40</v>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>每次升级</t>
+          <t>ARENA_RADIUS=40，圆形竞技场</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>竞技场半径</t>
+          <t>出怪口</t>
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>ARENA_RADIUS=40，圆形竞技场</t>
+          <t>均匀分布8个出怪口(GATE_COUNT=8)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>出怪口</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>4</v>
+          <t>休整间隔</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>每3波</t>
+        </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>东南西北4个固定出怪口(gateAngles)</t>
+          <t>CONFIG.restEveryNWaves=3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>休整间隔</t>
+          <t>休整时长</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>每3波</t>
+          <t>20秒</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.restEveryNWaves=3</t>
+          <t>CONFIG.restDuration=20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>休整时长</t>
+          <t>小波次间隔</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>20秒</t>
+          <t>5秒</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.restDuration=20</t>
+          <t>小波次之间5秒间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>--- 武器数值 ---</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr"/>
+      <c r="C20" s="22" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>步枪伤害</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>WEAPONS[0].dmg, cooldown=0.12s</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>霰弹枪伤害</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>0.375×6</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>WEAPONS[1].dmg×pellets, cooldown=0.6s</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>能量刀伤害</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>WEAPONS[2].dmg, cooldown=0.3s, 近战范围3.5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>自动开火</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>默认开启</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>准心对准敌人自动射击，近战范围内自动挥砍</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>--- 道具 ---</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr"/>
+      <c r="C25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>导弹道具掉率</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>击杀普通怪物3%概率掉落</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>导弹伤害</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>8×波次系数</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>足以清除炮灰，打残队长</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>导弹对Boss</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>-15%最大HP</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Boss受固定百分比伤害</t>
         </is>
       </c>
     </row>

--- a/怪物机制数值表.xlsx
+++ b/怪物机制数值表.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="E1" s="11" t="inlineStr">
         <is>
-          <t>体型(size)</t>
+          <t>体型</t>
         </is>
       </c>
       <c r="F1" s="11" t="inlineStr">
@@ -720,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>4</v>
@@ -780,7 +780,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="H3" s="14" t="n">
         <v>5</v>
@@ -798,7 +798,7 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>自爆(8m范围)</t>
+          <t>自爆(8m范围)+连锁爆炸</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0.6</v>
+        <v>1.44</v>
       </c>
       <c r="H4" s="14" t="n">
         <v>8</v>
@@ -960,7 +960,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.7</v>
+        <v>1.68</v>
       </c>
       <c r="H6" s="17" t="n">
         <v>25</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="N6" s="17" t="inlineStr">
         <is>
-          <t>Wave 6+</t>
+          <t>Wave 4+</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         <v>12</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0.7</v>
+        <v>1.68</v>
       </c>
       <c r="H7" s="14" t="n">
         <v>25</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>Wave 6+</t>
+          <t>Wave 4+</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="N8" s="18" t="inlineStr">
         <is>
-          <t>Wave 10+</t>
+          <t>Wave 8+</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         <v>45</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="H9" s="14" t="n">
         <v>40</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>Wave 10+</t>
+          <t>Wave 8+</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0.8</v>
+        <v>1.92</v>
       </c>
       <c r="H10" s="14" t="n">
         <v>35</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="N10" s="14" t="inlineStr">
         <is>
-          <t>Wave 10+</t>
+          <t>Wave 8+</t>
         </is>
       </c>
     </row>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>75(基础)+Lv×50(spawnFinalBoss)</t>
+          <t>75(基础)+Lv×50</t>
         </is>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.54</v>
+        <v>1.3</v>
       </c>
       <c r="H11" s="19" t="n">
         <v>500</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
-          <t>第一波基础怪物数量(baseCount=60,已翻倍)</t>
+          <t>第一波基础怪物数量(baseCount=60)</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>0.8-wave×0.03(最低0.12)</t>
+          <t>0.27-wave×0.01(最低0.04)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>波次越高刷怪越快</t>
+          <t>极速刷怪模式</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>20秒</t>
+          <t>15秒</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.restDuration=20</t>
+          <t>CONFIG.restDuration=15</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5秒</t>
+          <t>3秒</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>小波次之间5秒间隔</t>
+          <t>波次之间3秒间隔</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>第15波</t>
+          <t>第12波</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.bossUnlockWave=15</t>
+          <t>CONFIG.bossUnlockWave=12</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>第25波</t>
+          <t>第20波</t>
         </is>
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>CONFIG.bossWave=25</t>
+          <t>CONFIG.bossWave=20</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>炮灰中月球丧尸(+20%权重)</t>
+          <t>炮灰中月球丧尸</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>炮灰中虫潮基底(不变)</t>
+          <t>炮灰中虫潮基底</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>炮灰中自爆丧尸(+20%权重)</t>
+          <t>炮灰中自爆丧尸</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>炮灰中胖子丧尸(-20%权重)</t>
+          <t>炮灰中胖子丧尸</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>队长出现(Wave6+)</t>
+          <t>队长出现(Wave4+)</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>min(10%, 3%+(wave-6)×1%)</t>
+          <t>min(10%, 3%+(wave-4)×1%)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>精英出现(Wave10+)</t>
+          <t>精英出现(Wave8+)</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>min(12%, 2%+(wave-10)×1%)</t>
+          <t>min(12%, 2%+(wave-8)×1%)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>移速0.54(已降为1/4)</t>
+          <t>移速1.3</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>每250ms召唤一只，带波次系数，紫色召唤光柱</t>
+          <t>每250ms召唤一只，带波次系数</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>先扣护盾再扣血，击退6力度，冲击波动画</t>
+          <t>先扣护盾再扣血，击退6力度</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>30秒CD，蓝色护盾球视觉效果</t>
+          <t>30秒CD，蓝色护盾球视觉</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>spawnFinalBoss: 500+gameState.level*50</t>
+          <t>spawnFinalBoss动态计算</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>动态计算(ENEMY_TYPES中hp=75为占位)</t>
+          <t>ENEMY_TYPES中hp=75为占位</t>
         </is>
       </c>
     </row>
@@ -1927,11 +1927,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>spawnFinalBoss中</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -1952,11 +1948,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>spawnFinalBoss中</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1969,7 +1961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2039,7 +2031,7 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>持能量刀时移动加速(WEAPONS[2].speedBonus)</t>
+          <t>持能量刀时移动加速</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2046,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>垂直跳跃速度(player.jumpSpeed)</t>
+          <t>垂直跳跃速度</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2061,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>下落加速度(player.gravity)</t>
+          <t>下落加速度</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2076,7 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>初始生命值(gameState.hp)</t>
+          <t>初始生命值</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2091,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>自动回复，受击后4秒开始(gameState.shield)</t>
+          <t>自动回复，受击后4秒开始</t>
         </is>
       </c>
     </row>
@@ -2116,169 +2108,169 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>4秒无伤后开始回复(gameState.shieldRegen)</t>
+          <t>4秒无伤后开始回复</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>护盾回复延迟</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>4秒</t>
-        </is>
+          <t>复活次数</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>受击后N秒才开始回复(gameState.shieldDelay)</t>
+          <t>阶段一最大复活次数，阶段二无复活</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>复活次数</t>
+          <t>初始经验(Lv1→2)</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>阶段一最大复活次数(CONFIG.maxRevives)，阶段二无复活</t>
+          <t>CONFIG.expBase=24(降低20%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>初始经验(Lv1→2)</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>30</v>
+          <t>经验增长率</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>×1.18/级</t>
+        </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.expBase=30</t>
+          <t>CONFIG.expGrowth=1.18(平滑曲线)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>经验增长率</t>
+          <t>升级奖励</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>×1.18/级</t>
+          <t>+25金 +20HP +5%伤害</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.expGrowth=1.18(平滑曲线)</t>
+          <t>每次升级</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>升级奖励</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>+25金 +20HP +5%伤害</t>
-        </is>
+          <t>竞技场半径</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>40</v>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>每次升级</t>
+          <t>ARENA_RADIUS=40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>竞技场半径</t>
+          <t>出怪口</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>ARENA_RADIUS=40，圆形竞技场</t>
+          <t>均匀分布8个出怪口</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>出怪口</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>8</v>
+          <t>休整间隔</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>每3波</t>
+        </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>均匀分布8个出怪口(GATE_COUNT=8)</t>
+          <t>CONFIG.restEveryNWaves=3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>休整间隔</t>
+          <t>休整时长</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>每3波</t>
+          <t>15秒</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.restEveryNWaves=3</t>
+          <t>CONFIG.restDuration=15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>休整时长</t>
+          <t>小波次间隔</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>20秒</t>
+          <t>3秒</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.restDuration=20</t>
+          <t>波次之间3秒间隔</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>小波次间隔</t>
+          <t>一局时长</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>5秒</t>
+          <t>约15分钟</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>小波次之间5秒间隔</t>
+          <t>方案C极速刷怪模式</t>
         </is>
       </c>
     </row>
@@ -2298,11 +2290,11 @@
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>WEAPONS[0].dmg, cooldown=0.12s</t>
+          <t>cooldown=0.12s</t>
         </is>
       </c>
     </row>
@@ -2314,12 +2306,12 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>0.375×6</t>
+          <t>0.5625×6</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>WEAPONS[1].dmg×pellets, cooldown=0.6s</t>
+          <t>cooldown=0.6s, 6弹丸</t>
         </is>
       </c>
     </row>
@@ -2330,11 +2322,11 @@
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>WEAPONS[2].dmg, cooldown=0.3s, 近战范围3.5m</t>
+          <t>cooldown=0.3s, 近战范围3.5m</t>
         </is>
       </c>
     </row>
@@ -2412,6 +2404,83 @@
       <c r="C28" s="20" t="inlineStr">
         <is>
           <t>Boss受固定百分比伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>--- 经验球 ---</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr"/>
+      <c r="C29" s="22" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>经验球</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>击杀掉落</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>蓝色发光球，永不消失</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>吸附范围</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>基础~16m</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>磁吸范围，含词条增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>拾取范围</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>基础~7.5m</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>含词条增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>大经验球</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>导弹轰炸合并</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>最大100倍大小，2秒不可吸附期</t>
         </is>
       </c>
     </row>

--- a/怪物机制数值表.xlsx
+++ b/怪物机制数值表.xlsx
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
-          <t>第一波基础怪物数量(baseCount=60)</t>
+          <t>第一波基础怪物数量(baseCount=48)</t>
         </is>
       </c>
     </row>
@@ -1352,11 +1352,11 @@
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>每波数量 = 60 × 1.22^(wave-1)</t>
+          <t>每波数量 = 48 × 1.15^(wave-1)</t>
         </is>
       </c>
     </row>
@@ -1380,283 +1380,397 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>刷怪间隔</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>0.27-wave×0.01(最低0.04)</t>
-        </is>
+          <t>出怪上限</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>200</v>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>极速刷怪模式</t>
+          <t>单波最多200只怪物</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>波次系数(血量)</t>
+          <t>刷怪间隔</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>1+(wave-1)×0.15</t>
+          <t>0.1秒</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>每波怪物血量增加15%</t>
+          <t>固定0.1秒间隔</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>击杀经验</t>
+          <t>批量生成</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>10(base)</t>
+          <t>5只/次</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.expPerKillBase=10</t>
+          <t>每次间隔生成5只</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>休整触发</t>
+          <t>波次系数(血量)</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>每3波</t>
+          <t>1+(wave-1)×0.40</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.restEveryNWaves=3</t>
+          <t>每波怪物血量增加40%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>休整时长</t>
+          <t>击杀经验系数</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>15秒</t>
+          <t>score×0.1</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.restDuration=15</t>
+          <t>每只怪经验=分数×0.1(保底1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>小波次间隔</t>
+          <t>休整触发</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>3秒</t>
+          <t>每3波</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>波次之间3秒间隔</t>
+          <t>CONFIG.restEveryNWaves=3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Boss门解锁</t>
+          <t>休整时长</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>第12波</t>
+          <t>15秒</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.bossUnlockWave=12</t>
+          <t>CONFIG.restDuration=15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>自动Boss波</t>
+          <t>小波次间隔</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>第20波</t>
+          <t>3秒</t>
         </is>
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>CONFIG.bossWave=20</t>
+          <t>波次之间3秒间隔</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>出怪口数量</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>8</v>
+          <t>Boss门解锁</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>第12波</t>
+        </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>GATE_COUNT=8</t>
+          <t>CONFIG.bossUnlockWave=12</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>--- 出怪分配 ---</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr"/>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>--- 按概率分配 ---</t>
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>自动Boss波</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>第20波</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>CONFIG.bossWave=20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>炮灰比例</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>100%-队长%-精英%</t>
-        </is>
+          <t>出怪口数量</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>8</v>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>剩余全部为炮灰</t>
+          <t>GATE_COUNT=8</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  zombie</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>~46%(权重55)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>炮灰中月球丧尸</t>
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>--- 出怪分配 ---</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>--- 按概率分配 ---</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  swarm</t>
+          <t>炮灰比例</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>~17%(权重20)</t>
+          <t>100%-队长%-精英%</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>炮灰中虫潮基底</t>
+          <t>剩余全部为炮灰</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  bomber</t>
+          <t xml:space="preserve">  zombie</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>~33%(权重40)</t>
+          <t>~46%(权重55)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>炮灰中自爆丧尸</t>
+          <t>炮灰中月球丧尸</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  fatso</t>
+          <t xml:space="preserve">  swarm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>~4%(权重5)</t>
+          <t>~17%(权重20)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>炮灰中胖子丧尸</t>
+          <t>炮灰中虫潮基底</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>队长出现(Wave4+)</t>
+          <t xml:space="preserve">  bomber</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>min(10%, 3%+(wave-4)×1%)</t>
+          <t>~33%(权重40)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>医疗/护盾各50%</t>
+          <t>炮灰中自爆丧尸</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  fatso</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>~4%(权重5)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>炮灰中胖子丧尸</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>队长出现(Wave4+)</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>min(10%, 3%+(wave-4)×1%)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>医疗/护盾各50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
           <t>精英出现(Wave8+)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>min(12%, 2%+(wave-8)×1%)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>刺客/坦克/远程均匀分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>--- 升级系统 ---</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr"/>
+      <c r="C24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>expBase</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>升到2级所需经验(80×0.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>expGrowth</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>每级经验倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>升级奖励</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>+25金 +20HP +5%伤害</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>每次升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>--- 治疗系统 ---</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr"/>
+      <c r="C28" s="22" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>医疗队长治疗量</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>8%最大HP/3秒</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>治疗周围8m内怪物</t>
         </is>
       </c>
     </row>
@@ -1889,12 +2003,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>500+Lv×50</t>
+          <t>(500+Lv×50)×2</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>spawnFinalBoss动态计算</t>
+          <t>spawnFinalBoss动态计算，血量翻倍</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -2134,11 +2248,11 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>CONFIG.expBase=24(降低20%)</t>
+          <t>CONFIG.expBase=64(原80×0.8)</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2379,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>约15分钟</t>
+          <t>约8-9分钟</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>方案C极速刷怪模式</t>
+          <t>优化后出怪48基数/上限200/批量5只</t>
         </is>
       </c>
     </row>
